--- a/data/trans_bre/P36BPD07_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P36BPD07_R-Provincia-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,72</t>
+          <t>2,93</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 8,2</t>
+          <t>-3,99; 8,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 14,83</t>
+          <t>-3,12; 9,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 10,13</t>
+          <t>-4,52; 10,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 19,37</t>
+          <t>-3,64; 11,42</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,71</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 8,82</t>
+          <t>-0,13; 8,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 7,9</t>
+          <t>-3,8; 6,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 10,85</t>
+          <t>-0,2; 10,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 10,64</t>
+          <t>-4,6; 8,93</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7,07</t>
+          <t>7,96</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 5,34</t>
+          <t>0,15; 5,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 13,13</t>
+          <t>3,45; 13,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 5,72</t>
+          <t>0,15; 5,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 17,16</t>
+          <t>4,1; 17,36</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,27</t>
+          <t>1,82</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 11,09</t>
+          <t>-0,27; 10,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 12,97</t>
+          <t>-4,9; 8,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 14,85</t>
+          <t>-0,35; 14,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 16,6</t>
+          <t>-5,58; 11,47</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11,28</t>
+          <t>10,81</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 12,13</t>
+          <t>-1,86; 12,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 18,12</t>
+          <t>4,62; 17,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 16,13</t>
+          <t>-2,24; 16,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,72; 25,89</t>
+          <t>5,82; 24,84</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7,2</t>
+          <t>7,02</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 9,55</t>
+          <t>-1,37; 9,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,34; 11,96</t>
+          <t>2,56; 11,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 11,56</t>
+          <t>-1,49; 11,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,6; 14,55</t>
+          <t>2,89; 14,26</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6,95</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 0,54</t>
+          <t>-7,99; 0,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 16,4</t>
+          <t>-3,92; 5,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 0,57</t>
+          <t>-9,12; 0,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 21,58</t>
+          <t>-4,7; 6,87</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-8,09</t>
+          <t>9,09</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-14,78%</t>
+          <t>23,87%</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 7,21</t>
+          <t>-0,44; 6,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-32,89; 9,8</t>
+          <t>3,83; 13,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 9,06</t>
+          <t>-0,54; 8,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-42,11; 26,37</t>
+          <t>9,11; 37,92</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5,07</t>
+          <t>4,83</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -1081,22 +1081,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,23</t>
+          <t>0,64; 3,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 9,2</t>
+          <t>2,74; 6,99</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,76; 5,04</t>
+          <t>0,74; 4,73</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 12,73</t>
+          <t>3,77; 9,94</t>
         </is>
       </c>
     </row>
